--- a/Model objective analysis/Capacity increase/L shape base model 35 scenarios/L_Shape_base_35_tender_fixed.xlsx
+++ b/Model objective analysis/Capacity increase/L shape base model 35 scenarios/L_Shape_base_35_tender_fixed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -935,18 +935,18 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -998,18 +998,18 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Hepatitis_B</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1019,18 +1019,18 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Hepatitis_B</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1061,18 +1061,18 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hepatitis_B</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1082,18 +1082,18 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hepatitis_B</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>404</v>
+        <v>439</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1124,18 +1124,18 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1145,18 +1145,18 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1166,104 +1166,20 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>428</v>
+        <v>478</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E36" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>439</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" t="n">
-        <v>8</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>465</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>9</v>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>478</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" t="inlineStr">
         <is>
           <t>Full</t>
         </is>

--- a/Model objective analysis/Capacity increase/L shape base model 35 scenarios/L_Shape_base_35_tender_fixed.xlsx
+++ b/Model objective analysis/Capacity increase/L shape base model 35 scenarios/L_Shape_base_35_tender_fixed.xlsx
@@ -452,7 +452,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -473,7 +473,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
         <v>10</v>
@@ -956,7 +956,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
